--- a/data/trans_bre/MCS12_SP_R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R3-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 15,46</t>
+          <t>1,38; 15,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,87; 28,78</t>
+          <t>12,36; 29,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 20,46</t>
+          <t>3,97; 20,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 4,05</t>
+          <t>-3,11; 4,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 106,48</t>
+          <t>6,43; 117,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,24; 99,58</t>
+          <t>34,6; 103,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,7; 77,43</t>
+          <t>10,62; 77,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 93,96</t>
+          <t>-37,08; 94,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 20,02</t>
+          <t>8,36; 20,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 16,02</t>
+          <t>4,96; 15,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,75</t>
+          <t>3,26; 11,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 13,36</t>
+          <t>3,5; 13,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,6; 87,14</t>
+          <t>27,77; 87,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,89; 125,52</t>
+          <t>29,67; 127,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,08; 157,18</t>
+          <t>31,13; 163,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 103,87</t>
+          <t>18,57; 106,83</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 10,87</t>
+          <t>3,03; 10,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 14,89</t>
+          <t>2,82; 14,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 9,62</t>
+          <t>0,11; 9,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 11,5</t>
+          <t>1,62; 11,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>44,61; 487,99</t>
+          <t>45,01; 496,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,88; 122,83</t>
+          <t>15,97; 129,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 120,02</t>
+          <t>0,23; 124,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 105,67</t>
+          <t>9,71; 111,45</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 11,61</t>
+          <t>1,9; 11,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,04; 27,34</t>
+          <t>13,76; 26,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 19,42</t>
+          <t>6,63; 19,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 11,3</t>
+          <t>-3,49; 11,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,93; 153,11</t>
+          <t>13,71; 145,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,34; 142,79</t>
+          <t>52,37; 136,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,01; 122,4</t>
+          <t>28,28; 118,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 114,65</t>
+          <t>-20,63; 116,48</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 17,07</t>
+          <t>-1,05; 17,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 26,22</t>
+          <t>10,66; 26,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 19,12</t>
+          <t>0,17; 19,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 19,75</t>
+          <t>3,4; 20,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 66,59</t>
+          <t>-2,96; 66,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,82; 262,81</t>
+          <t>61,72; 283,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 54,75</t>
+          <t>0,32; 52,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,75; 45,21</t>
+          <t>6,35; 46,38</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 15,0</t>
+          <t>4,73; 14,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,62; 16,34</t>
+          <t>2,54; 16,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,47</t>
+          <t>4,67; 17,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 8,92</t>
+          <t>-1,8; 9,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,94; 452,62</t>
+          <t>59,72; 461,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,64; 123,01</t>
+          <t>12,0; 124,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,21; 184,81</t>
+          <t>29,89; 190,97</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 66,53</t>
+          <t>-10,08; 69,86</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 10,39</t>
+          <t>1,58; 10,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 9,47</t>
+          <t>-0,13; 9,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 14,22</t>
+          <t>3,87; 13,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 53,29</t>
+          <t>7,28; 52,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,4; 88,02</t>
+          <t>10,41; 90,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 56,14</t>
+          <t>-0,81; 54,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,98; 79,91</t>
+          <t>15,73; 76,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,68; 206,19</t>
+          <t>25,51; 213,19</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 10,65</t>
+          <t>1,01; 10,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 10,8</t>
+          <t>0,72; 10,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,77</t>
+          <t>-0,83; 7,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 25,21</t>
+          <t>6,3; 25,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 39,35</t>
+          <t>3,61; 38,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 35,08</t>
+          <t>1,95; 35,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 47,67</t>
+          <t>-4,32; 43,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,99; 351,76</t>
+          <t>25,92; 282,89</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,95</t>
+          <t>5,94; 9,87</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,78</t>
+          <t>8,09; 12,55</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,96</t>
+          <t>6,11; 10,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,09; 23,94</t>
+          <t>7,16; 25,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>28,56; 56,06</t>
+          <t>29,99; 56,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,85; 60,67</t>
+          <t>34,81; 59,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,23; 56,19</t>
+          <t>30,0; 55,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35,82; 140,26</t>
+          <t>35,98; 160,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R3-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R3-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 15,79</t>
+          <t>0,57; 15,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 29,51</t>
+          <t>11,25; 27,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 20,88</t>
+          <t>4,41; 20,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 4,21</t>
+          <t>-2,39; 4,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 117,31</t>
+          <t>2,43; 106,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,6; 103,35</t>
+          <t>31,26; 97,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 77,15</t>
+          <t>12,45; 78,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 94,4</t>
+          <t>-31,34; 97,42</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,56</t>
+          <t>8,35</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,36; 20,51</t>
+          <t>8,93; 20,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 15,73</t>
+          <t>5,24; 16,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 11,31</t>
+          <t>2,81; 11,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 13,57</t>
+          <t>3,99; 13,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,77; 87,85</t>
+          <t>29,98; 85,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,67; 127,7</t>
+          <t>29,3; 138,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,13; 163,79</t>
+          <t>24,64; 162,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,57; 106,83</t>
+          <t>20,47; 104,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 10,87</t>
+          <t>3,01; 10,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 14,83</t>
+          <t>2,4; 14,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 9,69</t>
+          <t>0,26; 10,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 11,45</t>
+          <t>0,77; 11,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,01; 496,98</t>
+          <t>45,18; 502,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,97; 129,06</t>
+          <t>12,63; 121,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 124,05</t>
+          <t>-1,96; 131,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,71; 111,45</t>
+          <t>5,48; 111,0</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>8,63</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,62</t>
+          <t>1,78; 11,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,76; 26,47</t>
+          <t>12,73; 26,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 19,59</t>
+          <t>6,03; 18,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 11,56</t>
+          <t>2,67; 14,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,71; 145,75</t>
+          <t>13,23; 150,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,37; 136,42</t>
+          <t>49,96; 140,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,28; 118,82</t>
+          <t>27,48; 116,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 116,48</t>
+          <t>14,47; 145,88</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,56</t>
+          <t>11,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 17,33</t>
+          <t>-2,17; 16,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,66; 26,78</t>
+          <t>10,51; 26,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 19,07</t>
+          <t>0,35; 18,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 20,0</t>
+          <t>3,91; 19,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 66,47</t>
+          <t>-5,81; 66,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,72; 283,61</t>
+          <t>61,98; 265,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 52,58</t>
+          <t>0,5; 54,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 46,38</t>
+          <t>7,66; 46,04</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,73; 14,74</t>
+          <t>4,56; 14,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 16,25</t>
+          <t>1,85; 16,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 17,72</t>
+          <t>4,51; 17,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 9,06</t>
+          <t>-0,66; 10,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,72; 461,37</t>
+          <t>64,13; 421,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,0; 124,53</t>
+          <t>9,93; 123,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,89; 190,97</t>
+          <t>28,58; 193,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 69,86</t>
+          <t>-3,73; 76,55</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,96</t>
+          <t>11,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>46,48%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 10,47</t>
+          <t>1,54; 10,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 9,32</t>
+          <t>0,24; 9,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 13,93</t>
+          <t>4,36; 14,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 52,09</t>
+          <t>6,33; 16,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,41; 90,04</t>
+          <t>9,57; 81,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 54,1</t>
+          <t>1,43; 61,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,73; 76,09</t>
+          <t>19,5; 79,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,51; 213,19</t>
+          <t>22,44; 73,52</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,57</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,56</t>
+          <t>1,06; 10,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 10,84</t>
+          <t>0,87; 10,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 7,48</t>
+          <t>-0,56; 7,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,3; 25,25</t>
+          <t>3,3; 11,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 38,3</t>
+          <t>2,81; 39,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 35,35</t>
+          <t>2,25; 34,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 43,6</t>
+          <t>-3,09; 42,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>25,92; 282,89</t>
+          <t>14,24; 59,02</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12,55</t>
+          <t>8,11</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,94; 9,87</t>
+          <t>5,82; 9,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,09; 12,55</t>
+          <t>8,43; 12,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,13</t>
+          <t>5,87; 9,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,16; 25,9</t>
+          <t>6,25; 10,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,99; 56,25</t>
+          <t>29,39; 56,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34,81; 59,19</t>
+          <t>35,6; 59,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,0; 55,94</t>
+          <t>29,06; 54,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35,98; 160,34</t>
+          <t>30,02; 54,01</t>
         </is>
       </c>
     </row>
